--- a/Output/triple_differences_combined_key_coefficients.xlsx
+++ b/Output/triple_differences_combined_key_coefficients.xlsx
@@ -56,10 +56,13 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">0.013 (0.039)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.195 (0.149)</t>
+    <t xml:space="preserve">0.018 (0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.218 (0.149)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-*</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_educ</t>
@@ -71,10 +74,10 @@
     <t xml:space="preserve">-0.098 (0.102)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.046** (0.020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.080 (0.087)</t>
+    <t xml:space="preserve">-0.040* (0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.109 (0.098)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
@@ -86,10 +89,10 @@
     <t xml:space="preserve">0.108 (0.357)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.034 (0.142)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.032 (0.493)</t>
+    <t xml:space="preserve">-0.034 (0.130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.079 (0.423)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_desempleado</t>
@@ -101,13 +104,13 @@
     <t xml:space="preserve">0.137 (5.436)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.632* (1.349)</t>
+    <t xml:space="preserve">2.519* (1.305)</t>
   </si>
   <si>
     <t xml:space="preserve">+*</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.931 (5.812)</t>
+    <t xml:space="preserve">-3.753 (5.597)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_en_pareja</t>
@@ -125,10 +128,13 @@
     <t xml:space="preserve">+**</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.897*** (0.326)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.284* (1.166)</t>
+    <t xml:space="preserve">-0.945*** (0.273)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.495** (1.162)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_hombre</t>
@@ -140,10 +146,10 @@
     <t xml:space="preserve">-7.793 (8.868)</t>
   </si>
   <si>
-    <t xml:space="preserve">4.085 (2.686)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.166 (10.565)</t>
+    <t xml:space="preserve">5.015* (2.681)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.121 (10.699)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
@@ -155,31 +161,10 @@
     <t xml:space="preserve">-2.034 (1.770)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.665 (0.474)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.007* (1.553)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mun_pre_all_share_rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.048 (0.070)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893*** (0.311)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.073 (0.066)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.088*** (0.290)</t>
+    <t xml:space="preserve">-0.536 (0.512)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.299* (1.734)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
@@ -191,10 +176,25 @@
     <t xml:space="preserve">1.815 (5.587)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651 (1.300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.454 (5.506)</t>
+    <t xml:space="preserve">0.624 (1.278)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.821 (5.230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popdensgeo2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007 (0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033 (0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.010 (0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033 (0.048)</t>
   </si>
 </sst>
 </file>
@@ -586,7 +586,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>7412</v>
@@ -594,19 +594,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -617,19 +617,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -640,19 +640,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -663,22 +663,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>7412</v>
@@ -686,19 +686,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -709,19 +709,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -732,22 +732,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>7467</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
         <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
       </c>
       <c r="G11" t="n">
         <v>7412</v>
@@ -778,19 +778,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -824,19 +824,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -847,22 +847,22 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
         <v>7412</v>
@@ -870,22 +870,22 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>7467</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -902,13 +902,13 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>55</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>7412</v>
@@ -931,10 +931,10 @@
         <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="19">
@@ -948,13 +948,13 @@
         <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
         <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
         <v>7412</v>
